--- a/diseases/d058/2015-2019.xlsx
+++ b/diseases/d058/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1809,6 +1824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1954,6 +1974,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2102,6 +2127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2842,6 +2872,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2987,6 +3022,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3135,6 +3175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3875,6 +3920,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4020,6 +4070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4168,6 +4223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4908,6 +4968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5201,6 +5266,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5349,6 +5419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6089,6 +6164,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6234,6 +6314,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6382,6 +6467,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7122,6 +7212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7267,6 +7362,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7415,6 +7515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8303,6 +8408,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8448,6 +8558,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8596,6 +8711,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9336,6 +9456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9481,6 +9606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9629,6 +9759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10369,6 +10504,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10514,6 +10654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10662,6 +10807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11550,6 +11700,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11695,6 +11850,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11843,6 +12003,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12583,6 +12748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12728,6 +12898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12876,6 +13051,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13616,6 +13796,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13909,6 +14094,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14057,6 +14247,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14797,6 +14992,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14942,6 +15142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15090,6 +15295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15830,6 +16040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15975,6 +16190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16123,6 +16343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16863,6 +17088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17156,6 +17386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17304,6 +17539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18044,6 +18284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18189,6 +18434,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18337,6 +18587,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19077,6 +19332,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19222,6 +19482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19370,6 +19635,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20110,6 +20380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20403,6 +20678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20551,6 +20831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21291,6 +21576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21436,6 +21726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21584,6 +21879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22324,6 +22624,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22469,6 +22774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22617,6 +22927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23505,6 +23820,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23650,6 +23970,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23798,6 +24123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24538,6 +24868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24683,6 +25018,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24831,6 +25171,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25571,6 +25916,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25716,6 +26066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25864,6 +26219,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26752,6 +27112,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26897,6 +27262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27045,6 +27415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27785,6 +28160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27930,6 +28310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28078,6 +28463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28818,6 +29208,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28963,6 +29358,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29111,6 +29511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29999,6 +30404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30144,6 +30554,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30292,6 +30707,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31032,6 +31452,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31177,6 +31602,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31325,6 +31755,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32065,6 +32500,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32210,6 +32650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32358,6 +32803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33246,6 +33696,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33391,6 +33846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33539,6 +33999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34279,6 +34744,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34424,6 +34894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34572,6 +35047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35312,6 +35792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35605,6 +36090,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35753,6 +36243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36493,6 +36988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36638,6 +37138,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36786,6 +37291,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37526,6 +38036,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37671,6 +38186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37819,6 +38339,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38559,6 +39084,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38852,6 +39382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39000,6 +39535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39740,6 +40280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39885,6 +40430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40033,6 +40583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40773,6 +41328,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40918,6 +41478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41066,6 +41631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41806,6 +42376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41951,6 +42526,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42099,6 +42679,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42987,6 +43572,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43132,6 +43722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43280,6 +43875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44020,6 +44620,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44165,6 +44770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44313,6 +44923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45053,6 +45668,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45346,6 +45966,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45494,6 +46119,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46234,6 +46864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46379,6 +47014,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46527,6 +47167,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47267,6 +47912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47412,6 +48062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47560,6 +48215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48448,6 +49108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48593,6 +49258,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48741,6 +49411,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49481,6 +50156,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49626,6 +50306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49774,6 +50459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50514,6 +51204,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50659,6 +51354,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50807,6 +51507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51695,6 +52400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51840,6 +52550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51988,6 +52703,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52728,6 +53448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52873,6 +53598,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53021,6 +53751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53761,6 +54496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54054,6 +54794,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54202,6 +54947,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54794,6 +55544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55087,6 +55842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55235,6 +55995,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55975,6 +56740,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56120,6 +56890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56268,6 +57043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57008,6 +57788,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57153,6 +57938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57301,6 +58091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58189,6 +58984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58334,6 +59134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58482,6 +59287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59222,6 +60032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59367,6 +60182,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59515,6 +60335,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60255,6 +61080,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60400,6 +61230,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60548,6 +61383,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61436,6 +62276,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61581,6 +62426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61729,6 +62579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62469,6 +63324,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62614,6 +63474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62762,6 +63627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63502,6 +64372,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63795,6 +64670,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63943,6 +64823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64683,6 +65568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64828,6 +65718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64974,6 +65869,11 @@
       <c r="S437" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO437" t="inlineStr">
